--- a/development/one_file_rosetta_output/CPCT02340081T_rosetta.xlsx
+++ b/development/one_file_rosetta_output/CPCT02340081T_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E384"/>
+  <dimension ref="A1:F384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -678,7 +696,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -741,7 +762,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -812,7 +836,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -840,7 +867,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -926,7 +956,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -954,7 +987,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1010,7 +1046,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1073,7 +1112,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1157,9 +1199,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1215,7 +1260,10 @@
       <c r="D15" s="4">
         <v>2</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1269,9 +1317,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1325,9 +1376,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1383,7 +1437,10 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1454,7 +1511,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1547,7 +1607,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1603,7 +1666,10 @@
       <c r="D21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1659,7 +1725,10 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1713,9 +1782,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1776,9 +1848,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1856,7 +1931,10 @@
       <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1934,7 +2012,10 @@
       <c r="D26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1962,7 +2043,10 @@
       <c r="D27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2048,7 +2132,10 @@
       <c r="D28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2074,9 +2161,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2175,9 +2265,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
         <v>2</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2278,7 +2371,10 @@
       <c r="D31" s="4">
         <v>3</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="4">
+        <v>3</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2379,7 +2475,10 @@
       <c r="D32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2480,7 +2579,10 @@
       <c r="D33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2596,7 +2698,10 @@
       <c r="D34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2650,9 +2755,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2708,7 +2816,10 @@
       <c r="D36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2771,7 +2882,10 @@
       <c r="D37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2799,7 +2913,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2827,7 +2944,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2855,7 +2975,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2883,7 +3006,10 @@
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2911,7 +3037,10 @@
       <c r="D42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2982,7 +3111,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3010,7 +3142,10 @@
       <c r="D44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3038,7 +3173,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3154,7 +3292,10 @@
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3270,7 +3411,10 @@
       <c r="D47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="4">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3324,9 +3468,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3389,7 +3536,10 @@
       <c r="D49" s="4">
         <v>2</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4">
+        <v>2</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3452,7 +3602,10 @@
       <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3480,7 +3633,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3506,9 +3662,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3536,7 +3695,10 @@
       <c r="D53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3607,7 +3769,10 @@
       <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3635,7 +3800,10 @@
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3698,7 +3866,10 @@
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3726,7 +3897,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3754,7 +3928,10 @@
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3782,7 +3959,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3810,7 +3990,10 @@
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3918,7 +4101,10 @@
       <c r="D61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3944,9 +4130,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>2</v>
+      </c>
+      <c r="E62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4000,9 +4189,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>2</v>
+      </c>
+      <c r="E63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4056,9 +4248,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>2</v>
+      </c>
+      <c r="E64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4121,7 +4316,10 @@
       <c r="D65" s="4">
         <v>2</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>2</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4184,7 +4382,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4270,7 +4471,10 @@
       <c r="D67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4298,7 +4502,10 @@
       <c r="D68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4326,7 +4533,10 @@
       <c r="D69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4354,7 +4564,10 @@
       <c r="D70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4380,9 +4593,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4498,7 +4714,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4526,7 +4745,10 @@
       <c r="D73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4554,7 +4776,10 @@
       <c r="D74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4582,7 +4807,10 @@
       <c r="D75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4610,7 +4838,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4673,7 +4904,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4744,7 +4978,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4845,7 +5082,10 @@
       <c r="D79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4873,7 +5113,10 @@
       <c r="D80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4979,9 +5222,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5009,7 +5255,10 @@
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5132,7 +5381,10 @@
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5160,7 +5412,10 @@
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5186,9 +5441,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>3</v>
+      </c>
+      <c r="E85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5216,7 +5474,10 @@
       <c r="D86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5244,7 +5505,10 @@
       <c r="D87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5272,7 +5536,10 @@
       <c r="D88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5298,9 +5565,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5408,7 +5678,10 @@
       <c r="D90" s="4">
         <v>2</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>2</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5516,7 +5789,10 @@
       <c r="D91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5630,9 +5906,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>2</v>
+      </c>
+      <c r="E92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5746,9 +6025,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>2</v>
+      </c>
+      <c r="E93" s="4">
         <v>1</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5864,7 +6146,10 @@
       <c r="D94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5892,7 +6177,10 @@
       <c r="D95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>1</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5948,7 +6236,10 @@
       <c r="D96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6002,9 +6293,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>4</v>
+      </c>
+      <c r="E97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6058,9 +6352,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>4</v>
+      </c>
+      <c r="E98" s="4">
         <v>2</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6114,9 +6411,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>4</v>
+      </c>
+      <c r="E99" s="4">
         <v>3</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6172,7 +6472,10 @@
       <c r="D100" s="4">
         <v>4</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="4">
+        <v>4</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6226,9 +6529,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>4</v>
+      </c>
+      <c r="E101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6282,9 +6588,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>4</v>
+      </c>
+      <c r="E102" s="4">
         <v>2</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6338,9 +6647,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>4</v>
+      </c>
+      <c r="E103" s="4">
         <v>3</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6396,7 +6708,10 @@
       <c r="D104" s="4">
         <v>4</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>4</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6450,9 +6765,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>5</v>
+      </c>
+      <c r="E105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6506,9 +6824,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>5</v>
+      </c>
+      <c r="E106" s="4">
         <v>2</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6562,9 +6883,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>5</v>
+      </c>
+      <c r="E107" s="4">
         <v>3</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6618,9 +6942,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>5</v>
+      </c>
+      <c r="E108" s="4">
         <v>4</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6676,7 +7003,10 @@
       <c r="D109" s="4">
         <v>5</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="4">
+        <v>5</v>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6730,9 +7060,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>5</v>
+      </c>
+      <c r="E110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6786,9 +7119,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>5</v>
+      </c>
+      <c r="E111" s="4">
         <v>2</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6842,9 +7178,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>5</v>
+      </c>
+      <c r="E112" s="4">
         <v>3</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6898,9 +7237,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>5</v>
+      </c>
+      <c r="E113" s="4">
         <v>4</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6956,7 +7298,10 @@
       <c r="D114" s="4">
         <v>5</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="4">
+        <v>5</v>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7012,7 +7357,10 @@
       <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7066,9 +7414,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>14</v>
+      </c>
+      <c r="E116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7122,9 +7473,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>14</v>
+      </c>
+      <c r="E117" s="4">
         <v>2</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7178,9 +7532,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>14</v>
+      </c>
+      <c r="E118" s="4">
         <v>3</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7234,9 +7591,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>14</v>
+      </c>
+      <c r="E119" s="4">
         <v>4</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7290,9 +7650,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>14</v>
+      </c>
+      <c r="E120" s="4">
         <v>5</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7346,9 +7709,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>14</v>
+      </c>
+      <c r="E121" s="4">
         <v>6</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7402,9 +7768,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>14</v>
+      </c>
+      <c r="E122" s="4">
         <v>7</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7458,9 +7827,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>14</v>
+      </c>
+      <c r="E123" s="4">
         <v>8</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7514,9 +7886,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>14</v>
+      </c>
+      <c r="E124" s="4">
         <v>9</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7570,9 +7945,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>14</v>
+      </c>
+      <c r="E125" s="4">
         <v>10</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7626,9 +8004,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>14</v>
+      </c>
+      <c r="E126" s="4">
         <v>11</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7682,9 +8063,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>14</v>
+      </c>
+      <c r="E127" s="4">
         <v>12</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7738,9 +8122,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>14</v>
+      </c>
+      <c r="E128" s="4">
         <v>13</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7796,7 +8183,10 @@
       <c r="D129" s="4">
         <v>14</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>14</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7850,9 +8240,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>3</v>
+      </c>
+      <c r="E130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7906,9 +8299,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>3</v>
+      </c>
+      <c r="E131" s="4">
         <v>2</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7964,7 +8360,10 @@
       <c r="D132" s="4">
         <v>3</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>3</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8018,9 +8417,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>3</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8074,9 +8476,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>3</v>
+      </c>
+      <c r="E134" s="4">
         <v>2</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8132,7 +8537,10 @@
       <c r="D135" s="4">
         <v>3</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4">
+        <v>3</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8186,9 +8594,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>2</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8244,7 +8655,10 @@
       <c r="D137" s="4">
         <v>2</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="4">
+        <v>2</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8298,9 +8712,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>10</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8354,9 +8771,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>10</v>
+      </c>
+      <c r="E139" s="4">
         <v>2</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8410,9 +8830,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>10</v>
+      </c>
+      <c r="E140" s="4">
         <v>3</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8466,9 +8889,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>10</v>
+      </c>
+      <c r="E141" s="4">
         <v>4</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8522,9 +8948,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>10</v>
+      </c>
+      <c r="E142" s="4">
         <v>5</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8578,9 +9007,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>10</v>
+      </c>
+      <c r="E143" s="4">
         <v>6</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8634,9 +9066,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>10</v>
+      </c>
+      <c r="E144" s="4">
         <v>7</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8690,9 +9125,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>10</v>
+      </c>
+      <c r="E145" s="4">
         <v>8</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8746,9 +9184,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>10</v>
+      </c>
+      <c r="E146" s="4">
         <v>9</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8804,7 +9245,10 @@
       <c r="D147" s="4">
         <v>10</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>10</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8858,9 +9302,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>5</v>
+      </c>
+      <c r="E148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8914,9 +9361,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>5</v>
+      </c>
+      <c r="E149" s="4">
         <v>2</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8970,9 +9420,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>5</v>
+      </c>
+      <c r="E150" s="4">
         <v>3</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9026,9 +9479,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>5</v>
+      </c>
+      <c r="E151" s="4">
         <v>4</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9084,7 +9540,10 @@
       <c r="D152" s="4">
         <v>5</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="4">
+        <v>5</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9138,9 +9597,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>2</v>
+      </c>
+      <c r="E153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9196,7 +9658,10 @@
       <c r="D154" s="4">
         <v>2</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="4">
+        <v>2</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9250,9 +9715,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>2</v>
+      </c>
+      <c r="E155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9308,7 +9776,10 @@
       <c r="D156" s="4">
         <v>2</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="4">
+        <v>2</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9362,9 +9833,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>6</v>
+      </c>
+      <c r="E157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9418,9 +9892,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>6</v>
+      </c>
+      <c r="E158" s="4">
         <v>2</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9474,9 +9951,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>6</v>
+      </c>
+      <c r="E159" s="4">
         <v>3</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9530,9 +10010,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>6</v>
+      </c>
+      <c r="E160" s="4">
         <v>4</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9586,9 +10069,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>6</v>
+      </c>
+      <c r="E161" s="4">
         <v>5</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9644,7 +10130,10 @@
       <c r="D162" s="4">
         <v>6</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="4">
+        <v>6</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9698,9 +10187,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>18</v>
+      </c>
+      <c r="E163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9754,9 +10246,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>18</v>
+      </c>
+      <c r="E164" s="4">
         <v>2</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9810,9 +10305,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>18</v>
+      </c>
+      <c r="E165" s="4">
         <v>3</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9866,9 +10364,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>18</v>
+      </c>
+      <c r="E166" s="4">
         <v>4</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9922,9 +10423,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>18</v>
+      </c>
+      <c r="E167" s="4">
         <v>5</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9978,9 +10482,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>18</v>
+      </c>
+      <c r="E168" s="4">
         <v>6</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10034,9 +10541,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>18</v>
+      </c>
+      <c r="E169" s="4">
         <v>7</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10090,9 +10600,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>18</v>
+      </c>
+      <c r="E170" s="4">
         <v>8</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10146,9 +10659,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>18</v>
+      </c>
+      <c r="E171" s="4">
         <v>9</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10202,9 +10718,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>18</v>
+      </c>
+      <c r="E172" s="4">
         <v>10</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10258,9 +10777,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>18</v>
+      </c>
+      <c r="E173" s="4">
         <v>11</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10314,9 +10836,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>18</v>
+      </c>
+      <c r="E174" s="4">
         <v>12</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10370,9 +10895,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>18</v>
+      </c>
+      <c r="E175" s="4">
         <v>13</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10426,9 +10954,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>18</v>
+      </c>
+      <c r="E176" s="4">
         <v>14</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10482,9 +11013,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>18</v>
+      </c>
+      <c r="E177" s="4">
         <v>15</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10538,9 +11072,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>18</v>
+      </c>
+      <c r="E178" s="4">
         <v>16</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10594,9 +11131,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>18</v>
+      </c>
+      <c r="E179" s="4">
         <v>17</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10652,7 +11192,10 @@
       <c r="D180" s="4">
         <v>18</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="4">
+        <v>18</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10706,9 +11249,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>2</v>
+      </c>
+      <c r="E181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10801,7 +11347,10 @@
       <c r="D182" s="4">
         <v>2</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="4">
+        <v>2</v>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10894,7 +11443,10 @@
       <c r="D183" s="4">
         <v>1</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="4">
+        <v>1</v>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10957,7 +11509,10 @@
       <c r="D184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="4">
+        <v>1</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11026,9 +11581,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>59</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11209,9 +11767,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>59</v>
+      </c>
+      <c r="E186" s="4">
         <v>2</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11347,9 +11908,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>59</v>
+      </c>
+      <c r="E187" s="4">
         <v>3</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11440,9 +12004,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>59</v>
+      </c>
+      <c r="E188" s="4">
         <v>4</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11563,9 +12130,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>59</v>
+      </c>
+      <c r="E189" s="4">
         <v>5</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11709,9 +12279,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>59</v>
+      </c>
+      <c r="E190" s="4">
         <v>6</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11840,9 +12413,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>59</v>
+      </c>
+      <c r="E191" s="4">
         <v>7</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12001,9 +12577,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>59</v>
+      </c>
+      <c r="E192" s="4">
         <v>8</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12109,9 +12688,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>59</v>
+      </c>
+      <c r="E193" s="4">
         <v>9</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12247,9 +12829,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>59</v>
+      </c>
+      <c r="E194" s="4">
         <v>10</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12415,9 +13000,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>59</v>
+      </c>
+      <c r="E195" s="4">
         <v>11</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12538,9 +13126,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>59</v>
+      </c>
+      <c r="E196" s="4">
         <v>12</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12669,9 +13260,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>59</v>
+      </c>
+      <c r="E197" s="4">
         <v>13</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12785,9 +13379,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>59</v>
+      </c>
+      <c r="E198" s="4">
         <v>14</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12931,9 +13528,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>59</v>
+      </c>
+      <c r="E199" s="4">
         <v>15</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13054,9 +13654,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>59</v>
+      </c>
+      <c r="E200" s="4">
         <v>16</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13200,9 +13803,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>59</v>
+      </c>
+      <c r="E201" s="4">
         <v>17</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13338,9 +13944,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>59</v>
+      </c>
+      <c r="E202" s="4">
         <v>18</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13536,9 +14145,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>59</v>
+      </c>
+      <c r="E203" s="4">
         <v>19</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13704,9 +14316,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>59</v>
+      </c>
+      <c r="E204" s="4">
         <v>20</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13829,7 +14444,10 @@
       <c r="D205" s="4">
         <v>1</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="4">
+        <v>1</v>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13907,7 +14525,10 @@
       <c r="D206" s="4">
         <v>1</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="4">
+        <v>1</v>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13968,9 +14589,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>2</v>
+      </c>
+      <c r="E207" s="4">
         <v>1</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14041,7 +14665,10 @@
       <c r="D208" s="4">
         <v>2</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>2</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14110,9 +14737,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>2</v>
+      </c>
+      <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14175,7 +14805,10 @@
       <c r="D210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="4">
+        <v>2</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14238,7 +14871,10 @@
       <c r="D211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E211" s="4">
+        <v>1</v>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14397,9 +15033,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>3</v>
+      </c>
+      <c r="E212" s="4">
         <v>1</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14468,9 +15107,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>3</v>
+      </c>
+      <c r="E213" s="4">
         <v>2</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14548,7 +15190,10 @@
       <c r="D214" s="4">
         <v>3</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="4">
+        <v>3</v>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14647,9 +15292,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>2</v>
+      </c>
+      <c r="E215" s="4">
         <v>1</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14712,7 +15360,10 @@
       <c r="D216" s="4">
         <v>2</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="4">
+        <v>2</v>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14781,9 +15432,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>10</v>
+      </c>
+      <c r="E217" s="4">
         <v>1</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14853,9 +15507,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>10</v>
+      </c>
+      <c r="E218" s="4">
         <v>2</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14925,9 +15582,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>10</v>
+      </c>
+      <c r="E219" s="4">
         <v>3</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14997,9 +15657,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>10</v>
+      </c>
+      <c r="E220" s="4">
         <v>4</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15069,9 +15732,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>10</v>
+      </c>
+      <c r="E221" s="4">
         <v>5</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15141,9 +15807,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>10</v>
+      </c>
+      <c r="E222" s="4">
         <v>6</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15213,9 +15882,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>10</v>
+      </c>
+      <c r="E223" s="4">
         <v>7</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15285,9 +15957,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>10</v>
+      </c>
+      <c r="E224" s="4">
         <v>8</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15357,9 +16032,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>10</v>
+      </c>
+      <c r="E225" s="4">
         <v>9</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15431,7 +16109,10 @@
       <c r="D226" s="4">
         <v>10</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4">
+        <v>10</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15501,9 +16182,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>54</v>
+      </c>
+      <c r="E227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15573,9 +16257,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>54</v>
+      </c>
+      <c r="E228" s="4">
         <v>2</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15645,9 +16332,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>54</v>
+      </c>
+      <c r="E229" s="4">
         <v>3</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15717,9 +16407,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>54</v>
+      </c>
+      <c r="E230" s="4">
         <v>4</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15789,9 +16482,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>54</v>
+      </c>
+      <c r="E231" s="4">
         <v>5</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15861,9 +16557,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>54</v>
+      </c>
+      <c r="E232" s="4">
         <v>6</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15933,9 +16632,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>54</v>
+      </c>
+      <c r="E233" s="4">
         <v>7</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16005,9 +16707,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>54</v>
+      </c>
+      <c r="E234" s="4">
         <v>8</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16077,9 +16782,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>54</v>
+      </c>
+      <c r="E235" s="4">
         <v>9</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16149,9 +16857,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>54</v>
+      </c>
+      <c r="E236" s="4">
         <v>10</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16221,9 +16932,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>54</v>
+      </c>
+      <c r="E237" s="4">
         <v>11</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16293,9 +17007,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>54</v>
+      </c>
+      <c r="E238" s="4">
         <v>12</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16365,9 +17082,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>54</v>
+      </c>
+      <c r="E239" s="4">
         <v>13</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16437,9 +17157,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>54</v>
+      </c>
+      <c r="E240" s="4">
         <v>14</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16509,9 +17232,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>54</v>
+      </c>
+      <c r="E241" s="4">
         <v>15</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16581,9 +17307,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>54</v>
+      </c>
+      <c r="E242" s="4">
         <v>16</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16653,9 +17382,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>54</v>
+      </c>
+      <c r="E243" s="4">
         <v>17</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16725,9 +17457,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>54</v>
+      </c>
+      <c r="E244" s="4">
         <v>18</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16797,9 +17532,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>54</v>
+      </c>
+      <c r="E245" s="4">
         <v>19</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16869,9 +17607,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>54</v>
+      </c>
+      <c r="E246" s="4">
         <v>20</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16941,9 +17682,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>2</v>
+      </c>
+      <c r="E247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16999,7 +17743,10 @@
       <c r="D248" s="4">
         <v>2</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="4">
+        <v>2</v>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17055,7 +17802,10 @@
       <c r="D249" s="4">
         <v>1</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="4">
+        <v>1</v>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17109,9 +17859,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>3</v>
+      </c>
+      <c r="E250" s="4">
         <v>1</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17165,9 +17918,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>3</v>
+      </c>
+      <c r="E251" s="4">
         <v>2</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17223,7 +17979,10 @@
       <c r="D252" s="4">
         <v>3</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="4">
+        <v>3</v>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17279,7 +18038,10 @@
       <c r="D253" s="4">
         <v>1</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E253" s="4">
+        <v>1</v>
+      </c>
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17335,7 +18097,10 @@
       <c r="D254" s="4">
         <v>1</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="E254" s="4">
+        <v>1</v>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17389,9 +18154,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>156</v>
+      </c>
+      <c r="E255" s="4">
         <v>1</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17445,9 +18213,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>156</v>
+      </c>
+      <c r="E256" s="4">
         <v>2</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17501,9 +18272,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>156</v>
+      </c>
+      <c r="E257" s="4">
         <v>3</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17557,9 +18331,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>156</v>
+      </c>
+      <c r="E258" s="4">
         <v>4</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17613,9 +18390,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>156</v>
+      </c>
+      <c r="E259" s="4">
         <v>5</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17669,9 +18449,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>156</v>
+      </c>
+      <c r="E260" s="4">
         <v>6</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17725,9 +18508,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>156</v>
+      </c>
+      <c r="E261" s="4">
         <v>7</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17781,9 +18567,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>156</v>
+      </c>
+      <c r="E262" s="4">
         <v>8</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17837,9 +18626,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>156</v>
+      </c>
+      <c r="E263" s="4">
         <v>9</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17893,9 +18685,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>156</v>
+      </c>
+      <c r="E264" s="4">
         <v>10</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17949,9 +18744,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>156</v>
+      </c>
+      <c r="E265" s="4">
         <v>11</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18005,9 +18803,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>156</v>
+      </c>
+      <c r="E266" s="4">
         <v>12</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18061,9 +18862,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>156</v>
+      </c>
+      <c r="E267" s="4">
         <v>13</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18117,9 +18921,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>156</v>
+      </c>
+      <c r="E268" s="4">
         <v>14</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18173,9 +18980,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>156</v>
+      </c>
+      <c r="E269" s="4">
         <v>15</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18229,9 +19039,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>156</v>
+      </c>
+      <c r="E270" s="4">
         <v>16</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18285,9 +19098,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>156</v>
+      </c>
+      <c r="E271" s="4">
         <v>17</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18341,9 +19157,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>156</v>
+      </c>
+      <c r="E272" s="4">
         <v>18</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18397,9 +19216,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>156</v>
+      </c>
+      <c r="E273" s="4">
         <v>19</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18453,9 +19275,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>156</v>
+      </c>
+      <c r="E274" s="4">
         <v>20</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18511,7 +19336,10 @@
       <c r="D275" s="4">
         <v>1</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="E275" s="4">
+        <v>1</v>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18581,9 +19409,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>3</v>
+      </c>
+      <c r="E276" s="4">
         <v>1</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18644,9 +19475,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>3</v>
+      </c>
+      <c r="E277" s="4">
         <v>2</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18709,7 +19543,10 @@
       <c r="D278" s="4">
         <v>3</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="E278" s="4">
+        <v>3</v>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18772,7 +19609,10 @@
       <c r="D279" s="4">
         <v>1</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E279" s="4">
+        <v>1</v>
+      </c>
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18843,7 +19683,10 @@
       <c r="D280" s="4">
         <v>1</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="4">
+        <v>1</v>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18919,9 +19762,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>11</v>
+      </c>
+      <c r="E281" s="4">
         <v>1</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19117,9 +19963,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>11</v>
+      </c>
+      <c r="E282" s="4">
         <v>2</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19225,9 +20074,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>11</v>
+      </c>
+      <c r="E283" s="4">
         <v>3</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19348,9 +20200,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>11</v>
+      </c>
+      <c r="E284" s="4">
         <v>4</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19456,9 +20311,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>11</v>
+      </c>
+      <c r="E285" s="4">
         <v>5</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19587,9 +20445,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>11</v>
+      </c>
+      <c r="E286" s="4">
         <v>6</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19733,9 +20594,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>11</v>
+      </c>
+      <c r="E287" s="4">
         <v>7</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19849,9 +20713,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>11</v>
+      </c>
+      <c r="E288" s="4">
         <v>8</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19987,9 +20854,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>11</v>
+      </c>
+      <c r="E289" s="4">
         <v>9</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20118,9 +20988,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>11</v>
+      </c>
+      <c r="E290" s="4">
         <v>10</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20258,7 +21131,10 @@
       <c r="D291" s="4">
         <v>11</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="4">
+        <v>11</v>
+      </c>
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20381,7 +21257,10 @@
       <c r="D292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="4">
+        <v>1</v>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20453,7 +21332,10 @@
       <c r="D293" s="4">
         <v>1</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="4">
+        <v>1</v>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20514,9 +21396,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>3</v>
+      </c>
+      <c r="E294" s="4">
         <v>1</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20630,9 +21515,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>3</v>
+      </c>
+      <c r="E295" s="4">
         <v>2</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20785,7 +21673,10 @@
       <c r="D296" s="4">
         <v>3</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="4">
+        <v>3</v>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20906,9 +21797,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>2</v>
+      </c>
+      <c r="E297" s="4">
         <v>1</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21016,7 +21910,10 @@
       <c r="D298" s="4">
         <v>2</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="4">
+        <v>2</v>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21154,7 +22051,10 @@
       <c r="D299" s="4">
         <v>1</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="4">
+        <v>1</v>
+      </c>
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21215,9 +22115,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>3</v>
+      </c>
+      <c r="E300" s="4">
         <v>1</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21338,9 +22241,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>3</v>
+      </c>
+      <c r="E301" s="4">
         <v>2</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21471,7 +22377,10 @@
       <c r="D302" s="4">
         <v>3</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="E302" s="4">
+        <v>3</v>
+      </c>
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21615,9 +22524,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>2</v>
+      </c>
+      <c r="E303" s="4">
         <v>1</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21689,7 +22601,10 @@
       <c r="D304" s="4">
         <v>2</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="E304" s="4">
+        <v>2</v>
+      </c>
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21759,9 +22674,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>3</v>
+      </c>
+      <c r="E305" s="4">
         <v>1</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21837,9 +22755,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>3</v>
+      </c>
+      <c r="E306" s="4">
         <v>2</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21917,7 +22838,10 @@
       <c r="D307" s="4">
         <v>3</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="E307" s="4">
+        <v>3</v>
+      </c>
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21986,9 +22910,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>9</v>
+      </c>
+      <c r="E308" s="4">
         <v>1</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22049,9 +22976,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>9</v>
+      </c>
+      <c r="E309" s="4">
         <v>2</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22112,9 +23042,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>9</v>
+      </c>
+      <c r="E310" s="4">
         <v>3</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22175,9 +23108,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>9</v>
+      </c>
+      <c r="E311" s="4">
         <v>4</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22238,9 +23174,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>9</v>
+      </c>
+      <c r="E312" s="4">
         <v>5</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22301,9 +23240,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>9</v>
+      </c>
+      <c r="E313" s="4">
         <v>6</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22364,9 +23306,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>9</v>
+      </c>
+      <c r="E314" s="4">
         <v>7</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22427,9 +23372,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>9</v>
+      </c>
+      <c r="E315" s="4">
         <v>8</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22492,7 +23440,10 @@
       <c r="D316" s="4">
         <v>9</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="4">
+        <v>9</v>
+      </c>
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22555,7 +23506,10 @@
       <c r="D317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="4">
+        <v>1</v>
+      </c>
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22631,9 +23585,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>6</v>
+      </c>
+      <c r="E318" s="4">
         <v>1</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22739,9 +23696,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>6</v>
+      </c>
+      <c r="E319" s="4">
         <v>2</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22832,9 +23792,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>6</v>
+      </c>
+      <c r="E320" s="4">
         <v>3</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22940,9 +23903,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>6</v>
+      </c>
+      <c r="E321" s="4">
         <v>4</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23003,9 +23969,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>6</v>
+      </c>
+      <c r="E322" s="4">
         <v>5</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23106,7 +24075,10 @@
       <c r="D323" s="4">
         <v>6</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="4">
+        <v>6</v>
+      </c>
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23175,9 +24147,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>5</v>
+      </c>
+      <c r="E324" s="4">
         <v>1</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23247,9 +24222,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>5</v>
+      </c>
+      <c r="E325" s="4">
         <v>2</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23319,9 +24297,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>5</v>
+      </c>
+      <c r="E326" s="4">
         <v>3</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23391,9 +24372,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>5</v>
+      </c>
+      <c r="E327" s="4">
         <v>4</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23465,7 +24449,10 @@
       <c r="D328" s="4">
         <v>5</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="E328" s="4">
+        <v>5</v>
+      </c>
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23537,7 +24524,10 @@
       <c r="D329" s="4">
         <v>1</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="4">
+        <v>1</v>
+      </c>
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23607,9 +24597,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>3</v>
+      </c>
+      <c r="E330" s="4">
         <v>1</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23670,9 +24663,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>3</v>
+      </c>
+      <c r="E331" s="4">
         <v>2</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23744,7 +24740,10 @@
       <c r="D332" s="4">
         <v>3</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="4">
+        <v>3</v>
+      </c>
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23814,9 +24813,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>6</v>
+      </c>
+      <c r="E333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23886,9 +24888,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>6</v>
+      </c>
+      <c r="E334" s="4">
         <v>2</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23958,9 +24963,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>6</v>
+      </c>
+      <c r="E335" s="4">
         <v>3</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24030,9 +25038,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>6</v>
+      </c>
+      <c r="E336" s="4">
         <v>4</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24102,9 +25113,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>6</v>
+      </c>
+      <c r="E337" s="4">
         <v>5</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24176,7 +25190,10 @@
       <c r="D338" s="4">
         <v>6</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="E338" s="4">
+        <v>6</v>
+      </c>
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24246,9 +25263,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>2</v>
+      </c>
+      <c r="E339" s="4">
         <v>1</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24320,7 +25340,10 @@
       <c r="D340" s="4">
         <v>2</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="E340" s="4">
+        <v>2</v>
+      </c>
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24392,7 +25415,10 @@
       <c r="D341" s="4">
         <v>1</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="E341" s="4">
+        <v>1</v>
+      </c>
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24462,9 +25488,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>3</v>
+      </c>
+      <c r="E342" s="4">
         <v>1</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24534,9 +25563,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>3</v>
+      </c>
+      <c r="E343" s="4">
         <v>2</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24608,7 +25640,10 @@
       <c r="D344" s="4">
         <v>3</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="E344" s="4">
+        <v>3</v>
+      </c>
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24678,9 +25713,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>3</v>
+      </c>
+      <c r="E345" s="4">
         <v>1</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24750,9 +25788,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>3</v>
+      </c>
+      <c r="E346" s="4">
         <v>2</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24824,7 +25865,10 @@
       <c r="D347" s="4">
         <v>3</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="E347" s="4">
+        <v>3</v>
+      </c>
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24894,9 +25938,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>2</v>
+      </c>
+      <c r="E348" s="4">
         <v>1</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24968,7 +26015,10 @@
       <c r="D349" s="4">
         <v>2</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="E349" s="4">
+        <v>2</v>
+      </c>
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25040,7 +26090,10 @@
       <c r="D350" s="4">
         <v>1</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="E350" s="4">
+        <v>1</v>
+      </c>
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25110,9 +26163,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>2</v>
+      </c>
+      <c r="E351" s="4">
         <v>1</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25184,7 +26240,10 @@
       <c r="D352" s="4">
         <v>2</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="E352" s="4">
+        <v>2</v>
+      </c>
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25254,9 +26313,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>2</v>
+      </c>
+      <c r="E353" s="4">
         <v>1</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25328,7 +26390,10 @@
       <c r="D354" s="4">
         <v>2</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="E354" s="4">
+        <v>2</v>
+      </c>
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25398,9 +26463,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>16</v>
+      </c>
+      <c r="E355" s="4">
         <v>1</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25470,9 +26538,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>16</v>
+      </c>
+      <c r="E356" s="4">
         <v>2</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25542,9 +26613,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>16</v>
+      </c>
+      <c r="E357" s="4">
         <v>3</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25614,9 +26688,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>16</v>
+      </c>
+      <c r="E358" s="4">
         <v>4</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25686,9 +26763,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>16</v>
+      </c>
+      <c r="E359" s="4">
         <v>5</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25758,9 +26838,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>16</v>
+      </c>
+      <c r="E360" s="4">
         <v>6</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25830,9 +26913,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>16</v>
+      </c>
+      <c r="E361" s="4">
         <v>7</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25902,9 +26988,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>16</v>
+      </c>
+      <c r="E362" s="4">
         <v>8</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25974,9 +27063,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>16</v>
+      </c>
+      <c r="E363" s="4">
         <v>9</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26046,9 +27138,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>16</v>
+      </c>
+      <c r="E364" s="4">
         <v>10</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26118,9 +27213,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>16</v>
+      </c>
+      <c r="E365" s="4">
         <v>11</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26190,9 +27288,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>16</v>
+      </c>
+      <c r="E366" s="4">
         <v>12</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26262,9 +27363,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>16</v>
+      </c>
+      <c r="E367" s="4">
         <v>13</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26334,9 +27438,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>16</v>
+      </c>
+      <c r="E368" s="4">
         <v>14</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26406,9 +27513,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>16</v>
+      </c>
+      <c r="E369" s="4">
         <v>15</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26480,7 +27590,10 @@
       <c r="D370" s="4">
         <v>16</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="E370" s="4">
+        <v>16</v>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26550,9 +27663,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>8</v>
+      </c>
+      <c r="E371" s="4">
         <v>1</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26622,9 +27738,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>8</v>
+      </c>
+      <c r="E372" s="4">
         <v>2</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26694,9 +27813,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>8</v>
+      </c>
+      <c r="E373" s="4">
         <v>3</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26766,9 +27888,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>8</v>
+      </c>
+      <c r="E374" s="4">
         <v>4</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26838,9 +27963,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>8</v>
+      </c>
+      <c r="E375" s="4">
         <v>5</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26910,9 +28038,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>8</v>
+      </c>
+      <c r="E376" s="4">
         <v>6</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26982,9 +28113,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>8</v>
+      </c>
+      <c r="E377" s="4">
         <v>7</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27056,7 +28190,10 @@
       <c r="D378" s="4">
         <v>8</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="E378" s="4">
+        <v>8</v>
+      </c>
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27126,9 +28263,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>4</v>
+      </c>
+      <c r="E379" s="4">
         <v>1</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27198,9 +28338,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>4</v>
+      </c>
+      <c r="E380" s="4">
         <v>2</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27270,9 +28413,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>4</v>
+      </c>
+      <c r="E381" s="4">
         <v>3</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27344,7 +28490,10 @@
       <c r="D382" s="4">
         <v>4</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="E382" s="4">
+        <v>4</v>
+      </c>
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27416,7 +28565,10 @@
       <c r="D383" s="4">
         <v>1</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="4">
+        <v>1</v>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27488,7 +28640,10 @@
       <c r="D384" s="4">
         <v>1</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="E384" s="4">
+        <v>1</v>
+      </c>
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27542,166 +28697,219 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="212">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
     <mergeCell ref="A64:A65"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
     <mergeCell ref="A89:A90"/>
     <mergeCell ref="B89:B90"/>
     <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
     <mergeCell ref="A97:A100"/>
     <mergeCell ref="B97:B100"/>
     <mergeCell ref="C97:C100"/>
+    <mergeCell ref="D97:D100"/>
     <mergeCell ref="A101:A104"/>
     <mergeCell ref="B101:B104"/>
     <mergeCell ref="C101:C104"/>
+    <mergeCell ref="D101:D104"/>
     <mergeCell ref="A105:A109"/>
     <mergeCell ref="B105:B109"/>
     <mergeCell ref="C105:C109"/>
+    <mergeCell ref="D105:D109"/>
     <mergeCell ref="A110:A114"/>
     <mergeCell ref="B110:B114"/>
     <mergeCell ref="C110:C114"/>
+    <mergeCell ref="D110:D114"/>
     <mergeCell ref="A116:A129"/>
     <mergeCell ref="B116:B129"/>
     <mergeCell ref="C116:C129"/>
+    <mergeCell ref="D116:D129"/>
     <mergeCell ref="A130:A132"/>
     <mergeCell ref="B130:B132"/>
     <mergeCell ref="C130:C132"/>
+    <mergeCell ref="D130:D132"/>
     <mergeCell ref="A133:A135"/>
     <mergeCell ref="B133:B135"/>
     <mergeCell ref="C133:C135"/>
+    <mergeCell ref="D133:D135"/>
     <mergeCell ref="A136:A137"/>
     <mergeCell ref="B136:B137"/>
     <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
     <mergeCell ref="A138:A147"/>
     <mergeCell ref="B138:B147"/>
     <mergeCell ref="C138:C147"/>
+    <mergeCell ref="D138:D147"/>
     <mergeCell ref="A148:A152"/>
     <mergeCell ref="B148:B152"/>
     <mergeCell ref="C148:C152"/>
+    <mergeCell ref="D148:D152"/>
     <mergeCell ref="A153:A154"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="C153:C154"/>
+    <mergeCell ref="D153:D154"/>
     <mergeCell ref="A155:A156"/>
     <mergeCell ref="B155:B156"/>
     <mergeCell ref="C155:C156"/>
+    <mergeCell ref="D155:D156"/>
     <mergeCell ref="A157:A162"/>
     <mergeCell ref="B157:B162"/>
     <mergeCell ref="C157:C162"/>
+    <mergeCell ref="D157:D162"/>
     <mergeCell ref="A163:A180"/>
     <mergeCell ref="B163:B180"/>
     <mergeCell ref="C163:C180"/>
+    <mergeCell ref="D163:D180"/>
     <mergeCell ref="A181:A182"/>
     <mergeCell ref="B181:B182"/>
     <mergeCell ref="C181:C182"/>
+    <mergeCell ref="D181:D182"/>
     <mergeCell ref="A185:A204"/>
     <mergeCell ref="B185:B204"/>
     <mergeCell ref="C185:C204"/>
+    <mergeCell ref="D185:D204"/>
     <mergeCell ref="A207:A208"/>
     <mergeCell ref="B207:B208"/>
     <mergeCell ref="C207:C208"/>
+    <mergeCell ref="D207:D208"/>
     <mergeCell ref="A209:A210"/>
     <mergeCell ref="B209:B210"/>
     <mergeCell ref="C209:C210"/>
+    <mergeCell ref="D209:D210"/>
     <mergeCell ref="A212:A214"/>
     <mergeCell ref="B212:B214"/>
     <mergeCell ref="C212:C214"/>
+    <mergeCell ref="D212:D214"/>
     <mergeCell ref="A215:A216"/>
     <mergeCell ref="B215:B216"/>
     <mergeCell ref="C215:C216"/>
+    <mergeCell ref="D215:D216"/>
     <mergeCell ref="A217:A226"/>
     <mergeCell ref="B217:B226"/>
     <mergeCell ref="C217:C226"/>
+    <mergeCell ref="D217:D226"/>
     <mergeCell ref="A227:A246"/>
     <mergeCell ref="B227:B246"/>
     <mergeCell ref="C227:C246"/>
+    <mergeCell ref="D227:D246"/>
     <mergeCell ref="A247:A248"/>
     <mergeCell ref="B247:B248"/>
     <mergeCell ref="C247:C248"/>
+    <mergeCell ref="D247:D248"/>
     <mergeCell ref="A250:A252"/>
     <mergeCell ref="B250:B252"/>
     <mergeCell ref="C250:C252"/>
+    <mergeCell ref="D250:D252"/>
     <mergeCell ref="A255:A274"/>
     <mergeCell ref="B255:B274"/>
     <mergeCell ref="C255:C274"/>
+    <mergeCell ref="D255:D274"/>
     <mergeCell ref="A276:A278"/>
     <mergeCell ref="B276:B278"/>
     <mergeCell ref="C276:C278"/>
+    <mergeCell ref="D276:D278"/>
     <mergeCell ref="A281:A291"/>
     <mergeCell ref="B281:B291"/>
     <mergeCell ref="C281:C291"/>
+    <mergeCell ref="D281:D291"/>
     <mergeCell ref="A294:A296"/>
     <mergeCell ref="B294:B296"/>
     <mergeCell ref="C294:C296"/>
+    <mergeCell ref="D294:D296"/>
     <mergeCell ref="A297:A298"/>
     <mergeCell ref="B297:B298"/>
     <mergeCell ref="C297:C298"/>
+    <mergeCell ref="D297:D298"/>
     <mergeCell ref="A300:A302"/>
     <mergeCell ref="B300:B302"/>
     <mergeCell ref="C300:C302"/>
+    <mergeCell ref="D300:D302"/>
     <mergeCell ref="A303:A304"/>
     <mergeCell ref="B303:B304"/>
     <mergeCell ref="C303:C304"/>
+    <mergeCell ref="D303:D304"/>
     <mergeCell ref="A305:A307"/>
     <mergeCell ref="B305:B307"/>
     <mergeCell ref="C305:C307"/>
+    <mergeCell ref="D305:D307"/>
     <mergeCell ref="A308:A316"/>
     <mergeCell ref="B308:B316"/>
     <mergeCell ref="C308:C316"/>
+    <mergeCell ref="D308:D316"/>
     <mergeCell ref="A318:A323"/>
     <mergeCell ref="B318:B323"/>
     <mergeCell ref="C318:C323"/>
+    <mergeCell ref="D318:D323"/>
     <mergeCell ref="A324:A328"/>
     <mergeCell ref="B324:B328"/>
     <mergeCell ref="C324:C328"/>
+    <mergeCell ref="D324:D328"/>
     <mergeCell ref="A330:A332"/>
     <mergeCell ref="B330:B332"/>
     <mergeCell ref="C330:C332"/>
+    <mergeCell ref="D330:D332"/>
     <mergeCell ref="A333:A338"/>
     <mergeCell ref="B333:B338"/>
     <mergeCell ref="C333:C338"/>
+    <mergeCell ref="D333:D338"/>
     <mergeCell ref="A339:A340"/>
     <mergeCell ref="B339:B340"/>
     <mergeCell ref="C339:C340"/>
+    <mergeCell ref="D339:D340"/>
     <mergeCell ref="A342:A344"/>
     <mergeCell ref="B342:B344"/>
     <mergeCell ref="C342:C344"/>
+    <mergeCell ref="D342:D344"/>
     <mergeCell ref="A345:A347"/>
     <mergeCell ref="B345:B347"/>
     <mergeCell ref="C345:C347"/>
+    <mergeCell ref="D345:D347"/>
     <mergeCell ref="A348:A349"/>
     <mergeCell ref="B348:B349"/>
     <mergeCell ref="C348:C349"/>
+    <mergeCell ref="D348:D349"/>
     <mergeCell ref="A351:A352"/>
     <mergeCell ref="B351:B352"/>
     <mergeCell ref="C351:C352"/>
+    <mergeCell ref="D351:D352"/>
     <mergeCell ref="A353:A354"/>
     <mergeCell ref="B353:B354"/>
     <mergeCell ref="C353:C354"/>
+    <mergeCell ref="D353:D354"/>
     <mergeCell ref="A355:A370"/>
     <mergeCell ref="B355:B370"/>
     <mergeCell ref="C355:C370"/>
+    <mergeCell ref="D355:D370"/>
     <mergeCell ref="A371:A378"/>
     <mergeCell ref="B371:B378"/>
     <mergeCell ref="C371:C378"/>
+    <mergeCell ref="D371:D378"/>
     <mergeCell ref="A379:A382"/>
     <mergeCell ref="B379:B382"/>
     <mergeCell ref="C379:C382"/>
+    <mergeCell ref="D379:D382"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
